--- a/data/trans_camb/P15B_tráfico-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P15B_tráfico-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,92</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-1,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,0</t>
+          <t>-2,43</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 15,67</t>
+          <t>-26,76; 14,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 7,59</t>
+          <t>-33,67; 8,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 18,41</t>
+          <t>-25,03; 17,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 8,59</t>
+          <t>-13,63; 9,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 8,65</t>
+          <t>-14,05; 8,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 7,01</t>
+          <t>-14,61; 6,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 9,06</t>
+          <t>-12,42; 8,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 4,3</t>
+          <t>-16,98; 4,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 7,48</t>
+          <t>-14,74; 7,35</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-14,21%</t>
+          <t>-9,08%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-13,29%</t>
+          <t>-11,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-17,79%</t>
+          <t>-14,45%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,11; 122,18</t>
+          <t>-62,56; 105,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-77,93; 54,55</t>
+          <t>-78,85; 69,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,48; 119,91</t>
+          <t>-61,18; 122,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-68,35; 208,56</t>
+          <t>-65,98; 236,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-80,84; 234,39</t>
+          <t>-79,73; 240,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,07; 169,24</t>
+          <t>-72,12; 163,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,61; 92,58</t>
+          <t>-48,99; 92,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,98; 48,39</t>
+          <t>-68,22; 46,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 80,33</t>
+          <t>-56,6; 72,56</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-9,77</t>
+          <t>-10,18</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-1,77</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-6,06</t>
+          <t>-6,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 3,66</t>
+          <t>-20,87; 4,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,01; 3,54</t>
+          <t>-22,74; 4,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 4,89</t>
+          <t>-22,79; 3,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 10,24</t>
+          <t>-26,35; 10,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 13,55</t>
+          <t>-25,29; 13,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 18,04</t>
+          <t>-20,81; 17,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 1,93</t>
+          <t>-18,67; 2,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 2,47</t>
+          <t>-19,1; 2,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 5,52</t>
+          <t>-18,06; 3,98</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-28,67%</t>
+          <t>-29,89%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,45%</t>
+          <t>-5,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,3%</t>
+          <t>-20,73%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,05; 14,37</t>
+          <t>-48,32; 16,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,11; 13,62</t>
+          <t>-53,95; 20,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,34; 21,66</t>
+          <t>-55,4; 14,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,12; 56,27</t>
+          <t>-58,17; 57,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,89; 75,67</t>
+          <t>-56,3; 73,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,53; 102,44</t>
+          <t>-48,94; 103,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,72; 7,99</t>
+          <t>-46,16; 9,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,73; 11,58</t>
+          <t>-47,88; 9,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,77; 21,78</t>
+          <t>-44,56; 16,27</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,11</t>
+          <t>8,64</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,44</t>
+          <t>-1,72</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>3,79</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 17,6</t>
+          <t>-36,49; 16,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 13,16</t>
+          <t>-41,81; 15,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 38,13</t>
+          <t>-23,9; 36,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-31,11; 30,74</t>
+          <t>-30,06; 30,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,43; 5,92</t>
+          <t>-50,85; 5,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-35,85; 18,41</t>
+          <t>-32,91; 21,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 17,36</t>
+          <t>-23,47; 16,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,83; 3,71</t>
+          <t>-36,11; 2,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 23,78</t>
+          <t>-17,42; 26,36</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-15,17%</t>
+          <t>-5,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,55; 123,28</t>
+          <t>-78,72; 127,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-89,91; 108,19</t>
+          <t>-87,33; 136,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,76; 287,95</t>
+          <t>-54,19; 281,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,29; 377,82</t>
+          <t>-63,92; 333,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-95,53; 109,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,1; 200,75</t>
+          <t>-64,0; 235,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,05; 95,99</t>
+          <t>-54,3; 112,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,35; 27,37</t>
+          <t>-81,41; 23,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-47,48; 151,97</t>
+          <t>-42,52; 168,81</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-5,42</t>
+          <t>-5,16</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,15</t>
+          <t>-3,02</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 3,11</t>
+          <t>-17,12; 3,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,25; -0,96</t>
+          <t>-22,28; 0,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 5,91</t>
+          <t>-16,99; 5,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 6,63</t>
+          <t>-12,59; 7,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 5,34</t>
+          <t>-14,48; 5,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 11,54</t>
+          <t>-8,98; 10,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 1,7</t>
+          <t>-12,71; 1,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-15,41; -0,37</t>
+          <t>-15,0; -0,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 4,63</t>
+          <t>-9,69; 4,46</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-16,77%</t>
+          <t>-15,96%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-11,5%</t>
+          <t>-11,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 14,5</t>
+          <t>-43,36; 13,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-54,93; -2,07</t>
+          <t>-55,29; 3,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-47,56; 22,71</t>
+          <t>-45,21; 23,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 47,86</t>
+          <t>-43,35; 55,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,7; 39,07</t>
+          <t>-52,03; 35,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,51; 86,34</t>
+          <t>-33,33; 70,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,21; 7,51</t>
+          <t>-39,07; 7,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,47; -1,77</t>
+          <t>-47,2; -1,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 20,54</t>
+          <t>-30,86; 19,9</t>
         </is>
       </c>
     </row>
